--- a/example data/group/PCA ID Info.xlsx
+++ b/example data/group/PCA ID Info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,252 +454,560 @@
           <t>PC 3</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PC 4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PC 5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PC 6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PC 7</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PC 8</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PC 9</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PC 10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5 mm</t>
+          <t>5mm</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.171685006473705</v>
+        <v>-1.010644281315046</v>
       </c>
       <c r="D2" t="n">
-        <v>1.882911821431299</v>
+        <v>-12.77946573798519</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7205503331477202</v>
+        <v>-1.077824292366578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.644491841383827</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.762032913970359</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.7695414749914766</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2077380984430696</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.936183555273776</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.1500622409348785</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-5.119491778986641</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5 mm</t>
+          <t>5mm</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>-6.265781165100379</v>
+        <v>-10.21648212538811</v>
       </c>
       <c r="D3" t="n">
-        <v>1.453356744258063</v>
+        <v>-19.84343916631967</v>
       </c>
       <c r="E3" t="n">
-        <v>2.351674129208635</v>
+        <v>-3.19203113019964</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03365031482845491</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.67140028869545</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.375103645918499</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-15.07373830871036</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.814378537103721</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.117755933368095</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.323130642169549</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5 mm</t>
+          <t>5mm</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.75092352487483</v>
+        <v>-1.444596080811272</v>
       </c>
       <c r="D4" t="n">
-        <v>4.898661951762356</v>
+        <v>-23.36041726073149</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.580497502030243</v>
+        <v>1.302045975350623</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.533632607627437</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.521953593523711</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6102376699202012</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.139774912776231</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-13.33327911251007</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-7.151178004954452</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3.070571555912339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5 mm</t>
+          <t>5mm</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.582094263041421</v>
+        <v>23.02413070070054</v>
       </c>
       <c r="D5" t="n">
-        <v>3.27835580696842</v>
+        <v>-24.22948366881312</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.100726714929438</v>
+        <v>-13.45483562946633</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.841997558552796</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-12.20538569440607</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.7428088996382936</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.906220601234481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.04467082450647</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.66569590945433</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.735216679269491</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12 mm</t>
+          <t>12mm</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>1.990111150162949</v>
+        <v>14.90019129908537</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.769251969030279</v>
+        <v>13.93847314046836</v>
       </c>
       <c r="E6" t="n">
-        <v>4.507046870786072</v>
+        <v>-3.898590194165701</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-6.684496839462893</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.304649135298047</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-6.882666499430933</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2.40988250639361</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.931940978056319</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-8.564071409982665</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-7.223067354887029</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12 mm</t>
+          <t>12mm</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>1.808750831551146</v>
+        <v>28.81828771394322</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.154125338271659</v>
+        <v>15.20487920386131</v>
       </c>
       <c r="E7" t="n">
-        <v>6.390228457180018</v>
+        <v>-3.31113547908022</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.23960451062885</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.668667828296792</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-10.41453238564702</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-4.601678128425942</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-7.91007488620843</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-2.063641743762983</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.40357618183297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12 mm</t>
+          <t>12mm</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.425456452670307</v>
+        <v>-10.20013493090532</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.418924125809197</v>
+        <v>-4.391626237433744</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.142111470688089</v>
+        <v>16.14764470958399</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-8.70988421283603</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.14737695158804</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-12.17407622006342</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.641542000145844</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.905863425703305</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.347671495971949</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.972193891128909</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12 mm</t>
+          <t>12mm</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>5.830523382655245</v>
+        <v>12.11115778953773</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05203417557722412</v>
+        <v>16.25774228835854</v>
       </c>
       <c r="E9" t="n">
-        <v>1.694614893216939</v>
+        <v>-18.95566531416996</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-16.78730822919657</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.66238854650264</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.48590889791863</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.400849259721426</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.519908231360448</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.716062485727749</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.985053744788931</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25 mm</t>
+          <t>25mm</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>2.16282127386464</v>
+        <v>1.817083333942907</v>
       </c>
       <c r="D10" t="n">
-        <v>2.21050332702033</v>
+        <v>15.3508872990267</v>
       </c>
       <c r="E10" t="n">
-        <v>9.972207148376267</v>
+        <v>12.58471028436305</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.49038405452056</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.053239619449684</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.77350027245496</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.229778567007657</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.217924637592945</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.500508890367663</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.7500348588729928</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25 mm</t>
+          <t>25mm</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>13.53060059614899</v>
+        <v>-45.79877321826371</v>
       </c>
       <c r="D11" t="n">
-        <v>14.78731885638936</v>
+        <v>11.40032260808423</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.653919160328483</v>
+        <v>-20.38522297087511</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.508136004800456</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-7.154678070603</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-4.334162850617016</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.638764944133795</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.566549071719746</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.6401856483795582</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.07848511890398742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25 mm</t>
+          <t>25mm</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>4.230738297852166</v>
+        <v>-4.359968371778318</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.352685698187364</v>
+        <v>9.560970558092441</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.546426014042648</v>
+        <v>13.37502778854406</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-4.663921056018242</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-3.778740453326901</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2416688878500223</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4.393400151361091</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-4.018563654818142</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.908893290687722</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-6.569530233626398</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25 mm</t>
+          <t>25mm</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>7.556901882459248</v>
+        <v>-7.70877320864783</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.389854977392194</v>
+        <v>5.577080063763106</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.947624756542371</v>
+        <v>9.494346537251189</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-14.2655847918566</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-8.554582292813002</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.914704841650731</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-6.914122203875197</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-5.373118833185254</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.74014897359958</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.110420193133904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25 mm</t>
+          <t>25mm</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>3.085492997466261</v>
+        <v>0.06852137989978356</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.478300574716341</v>
+        <v>-2.685923090371451</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.665016213354383</v>
+        <v>11.37152971523061</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.180701762972087</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-14.76098670958218</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.400001890375139</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.22815291530369</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.737433688126049</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-9.192086064426348</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.815893075864461</v>
       </c>
     </row>
   </sheetData>

--- a/example data/group/PCA ID Info.xlsx
+++ b/example data/group/PCA ID Info.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5mm</t>
+          <t>5 mm</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -503,511 +503,511 @@
         <v>-1.010644281315046</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.77946573798519</v>
+        <v>-12.77946573798521</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.077824292366578</v>
+        <v>-1.077824292366595</v>
       </c>
       <c r="F2" t="n">
-        <v>3.644491841383827</v>
+        <v>3.644491841383799</v>
       </c>
       <c r="G2" t="n">
-        <v>9.762032913970359</v>
+        <v>9.762032913970375</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7695414749914766</v>
+        <v>-0.7695414749914627</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2077380984430696</v>
+        <v>0.2077380984430202</v>
       </c>
       <c r="J2" t="n">
-        <v>1.936183555273776</v>
+        <v>1.9361835552738</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1500622409348785</v>
+        <v>-0.1500622409348738</v>
       </c>
       <c r="L2" t="n">
-        <v>-5.119491778986641</v>
+        <v>-5.119491778986665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5mm</t>
+          <t>5 mm</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.21648212538811</v>
+        <v>-10.2164821253881</v>
       </c>
       <c r="D3" t="n">
-        <v>-19.84343916631967</v>
+        <v>-19.84343916631966</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.19203113019964</v>
+        <v>-3.192031130199647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03365031482845491</v>
+        <v>0.03365031482844801</v>
       </c>
       <c r="G3" t="n">
-        <v>11.67140028869545</v>
+        <v>11.67140028869544</v>
       </c>
       <c r="H3" t="n">
-        <v>3.375103645918499</v>
+        <v>3.375103645918346</v>
       </c>
       <c r="I3" t="n">
-        <v>-15.07373830871036</v>
+        <v>-15.07373830871044</v>
       </c>
       <c r="J3" t="n">
-        <v>1.814378537103721</v>
+        <v>1.814378537103339</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.117755933368095</v>
+        <v>-1.117755933368068</v>
       </c>
       <c r="L3" t="n">
-        <v>5.323130642169549</v>
+        <v>5.323130642169558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5mm</t>
+          <t>5 mm</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.444596080811272</v>
+        <v>-1.444596080811269</v>
       </c>
       <c r="D4" t="n">
-        <v>-23.36041726073149</v>
+        <v>-23.3604172607315</v>
       </c>
       <c r="E4" t="n">
-        <v>1.302045975350623</v>
+        <v>1.302045975350598</v>
       </c>
       <c r="F4" t="n">
         <v>1.533632607627437</v>
       </c>
       <c r="G4" t="n">
-        <v>1.521953593523711</v>
+        <v>1.521953593523712</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6102376699202012</v>
+        <v>0.6102376699202211</v>
       </c>
       <c r="I4" t="n">
-        <v>8.139774912776231</v>
+        <v>8.139774912776552</v>
       </c>
       <c r="J4" t="n">
-        <v>-13.33327911251007</v>
+        <v>-13.33327911250987</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.151178004954452</v>
+        <v>-7.15117800495447</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.070571555912339</v>
+        <v>-3.070571555912355</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5mm</t>
+          <t>5 mm</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>23.02413070070054</v>
+        <v>23.02413070070061</v>
       </c>
       <c r="D5" t="n">
         <v>-24.22948366881312</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.45483562946633</v>
+        <v>-13.4548356294664</v>
       </c>
       <c r="F5" t="n">
-        <v>4.841997558552796</v>
+        <v>4.841997558552751</v>
       </c>
       <c r="G5" t="n">
-        <v>-12.20538569440607</v>
+        <v>-12.20538569440608</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7428088996382936</v>
+        <v>-0.7428088996382299</v>
       </c>
       <c r="I5" t="n">
-        <v>1.906220601234481</v>
+        <v>1.906220601234352</v>
       </c>
       <c r="J5" t="n">
-        <v>6.04467082450647</v>
+        <v>6.044670824506506</v>
       </c>
       <c r="K5" t="n">
-        <v>8.66569590945433</v>
+        <v>8.665695909454316</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.735216679269491</v>
+        <v>-1.735216679269467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12mm</t>
+          <t>12 mm</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90019129908537</v>
+        <v>14.90019129908539</v>
       </c>
       <c r="D6" t="n">
-        <v>13.93847314046836</v>
+        <v>13.93847314046838</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.898590194165701</v>
+        <v>-3.898590194165674</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.684496839462893</v>
+        <v>-6.684496839462914</v>
       </c>
       <c r="G6" t="n">
-        <v>4.304649135298047</v>
+        <v>4.304649135298023</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.882666499430933</v>
+        <v>-6.882666499430949</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.40988250639361</v>
+        <v>-2.409882506393833</v>
       </c>
       <c r="J6" t="n">
-        <v>8.931940978056319</v>
+        <v>8.931940978056293</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.564071409982665</v>
+        <v>-8.564071409982654</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.223067354887029</v>
+        <v>-7.223067354887013</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12mm</t>
+          <t>12 mm</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>28.81828771394322</v>
+        <v>28.81828771394321</v>
       </c>
       <c r="D7" t="n">
-        <v>15.20487920386131</v>
+        <v>15.20487920386134</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.31113547908022</v>
+        <v>-3.311135479080217</v>
       </c>
       <c r="F7" t="n">
-        <v>11.23960451062885</v>
+        <v>11.23960451062889</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.668667828296792</v>
+        <v>-3.668667828296781</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.41453238564702</v>
+        <v>-10.41453238564709</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.601678128425942</v>
+        <v>-4.601678128425647</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.91007488620843</v>
+        <v>-7.910074886208526</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.063641743762983</v>
+        <v>-2.063641743762971</v>
       </c>
       <c r="L7" t="n">
-        <v>6.40357618183297</v>
+        <v>6.403576181832947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12mm</t>
+          <t>12 mm</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.20013493090532</v>
+        <v>-10.20013493090531</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.391626237433744</v>
+        <v>-4.391626237433782</v>
       </c>
       <c r="E8" t="n">
-        <v>16.14764470958399</v>
+        <v>16.14764470958401</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.70988421283603</v>
+        <v>-8.709884212835991</v>
       </c>
       <c r="G8" t="n">
-        <v>7.14737695158804</v>
+        <v>7.14737695158799</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.17407622006342</v>
+        <v>-12.17407622006333</v>
       </c>
       <c r="I8" t="n">
-        <v>9.641542000145844</v>
+        <v>9.641542000145835</v>
       </c>
       <c r="J8" t="n">
-        <v>4.905863425703305</v>
+        <v>4.905863425703561</v>
       </c>
       <c r="K8" t="n">
-        <v>4.347671495971949</v>
+        <v>4.347671495971918</v>
       </c>
       <c r="L8" t="n">
-        <v>5.972193891128909</v>
+        <v>5.972193891128915</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12mm</t>
+          <t>12 mm</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>12.11115778953773</v>
+        <v>12.11115778953774</v>
       </c>
       <c r="D9" t="n">
-        <v>16.25774228835854</v>
+        <v>16.2577422883586</v>
       </c>
       <c r="E9" t="n">
-        <v>-18.95566531416996</v>
+        <v>-18.95566531416986</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.78730822919657</v>
+        <v>-16.78730822919664</v>
       </c>
       <c r="G9" t="n">
-        <v>8.66238854650264</v>
+        <v>8.662388546502651</v>
       </c>
       <c r="H9" t="n">
-        <v>10.48590889791863</v>
+        <v>10.48590889791869</v>
       </c>
       <c r="I9" t="n">
-        <v>6.400849259721426</v>
+        <v>6.400849259721404</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.519908231360448</v>
+        <v>-2.519908231360337</v>
       </c>
       <c r="K9" t="n">
-        <v>2.716062485727749</v>
+        <v>2.716062485727717</v>
       </c>
       <c r="L9" t="n">
-        <v>2.985053744788931</v>
+        <v>2.985053744788936</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25mm</t>
+          <t>25 mm</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>1.817083333942907</v>
+        <v>1.817083333942913</v>
       </c>
       <c r="D10" t="n">
-        <v>15.3508872990267</v>
+        <v>15.35088729902666</v>
       </c>
       <c r="E10" t="n">
-        <v>12.58471028436305</v>
+        <v>12.58471028436294</v>
       </c>
       <c r="F10" t="n">
-        <v>24.49038405452056</v>
+        <v>24.4903840545206</v>
       </c>
       <c r="G10" t="n">
-        <v>7.053239619449684</v>
+        <v>7.053239619449712</v>
       </c>
       <c r="H10" t="n">
-        <v>9.77350027245496</v>
+        <v>9.773500272455005</v>
       </c>
       <c r="I10" t="n">
-        <v>3.229778567007657</v>
+        <v>3.22977856700754</v>
       </c>
       <c r="J10" t="n">
-        <v>2.217924637592945</v>
+        <v>2.217924637593029</v>
       </c>
       <c r="K10" t="n">
-        <v>3.500508890367663</v>
+        <v>3.500508890367648</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7500348588729928</v>
+        <v>-0.7500348588729776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25mm</t>
+          <t>25 mm</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>-45.79877321826371</v>
+        <v>-45.79877321826365</v>
       </c>
       <c r="D11" t="n">
-        <v>11.40032260808423</v>
+        <v>11.40032260808425</v>
       </c>
       <c r="E11" t="n">
-        <v>-20.38522297087511</v>
+        <v>-20.38522297087516</v>
       </c>
       <c r="F11" t="n">
-        <v>8.508136004800456</v>
+        <v>8.508136004800411</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.154678070603</v>
+        <v>-7.154678070603008</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.334162850617016</v>
+        <v>-4.334162850616992</v>
       </c>
       <c r="I11" t="n">
-        <v>1.638764944133795</v>
+        <v>1.638764944133814</v>
       </c>
       <c r="J11" t="n">
-        <v>0.566549071719746</v>
+        <v>0.5665490717198041</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6401856483795582</v>
+        <v>-0.6401856483795617</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07848511890398742</v>
+        <v>0.07848511890398098</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25mm</t>
+          <t>25 mm</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.359968371778318</v>
+        <v>-4.359968371778324</v>
       </c>
       <c r="D12" t="n">
-        <v>9.560970558092441</v>
+        <v>9.560970558092432</v>
       </c>
       <c r="E12" t="n">
-        <v>13.37502778854406</v>
+        <v>13.37502778854409</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.663921056018242</v>
+        <v>-4.663921056018194</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.778740453326901</v>
+        <v>-3.778740453326909</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2416688878500223</v>
+        <v>-0.2416688878500512</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.393400151361091</v>
+        <v>-4.393400151360981</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.018563654818142</v>
+        <v>-4.018563654818252</v>
       </c>
       <c r="K12" t="n">
-        <v>4.908893290687722</v>
+        <v>4.908893290687752</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.569530233626398</v>
+        <v>-6.569530233626406</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25mm</t>
+          <t>25 mm</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.70877320864783</v>
+        <v>-7.708773208647825</v>
       </c>
       <c r="D13" t="n">
-        <v>5.577080063763106</v>
+        <v>5.5770800637631</v>
       </c>
       <c r="E13" t="n">
-        <v>9.494346537251189</v>
+        <v>9.494346537251252</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.2655847918566</v>
+        <v>-14.26558479185656</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.554582292813002</v>
+        <v>-8.55458229281302</v>
       </c>
       <c r="H13" t="n">
-        <v>1.914704841650731</v>
+        <v>1.914704841650648</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.914122203875197</v>
+        <v>-6.914122203875047</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.373118833185254</v>
+        <v>-5.373118833185416</v>
       </c>
       <c r="K13" t="n">
-        <v>4.74014897359958</v>
+        <v>4.74014897359959</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.110420193133904</v>
+        <v>-1.110420193133892</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25mm</t>
+          <t>25 mm</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06852137989978356</v>
+        <v>0.0685213798997901</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.685923090371451</v>
+        <v>-2.685923090371475</v>
       </c>
       <c r="E14" t="n">
-        <v>11.37152971523061</v>
+        <v>11.37152971523062</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.180701762972087</v>
+        <v>-3.18070176297205</v>
       </c>
       <c r="G14" t="n">
         <v>-14.76098670958218</v>
       </c>
       <c r="H14" t="n">
-        <v>9.400001890375139</v>
+        <v>9.400001890375199</v>
       </c>
       <c r="I14" t="n">
-        <v>2.22815291530369</v>
+        <v>2.228152915303401</v>
       </c>
       <c r="J14" t="n">
-        <v>6.737433688126049</v>
+        <v>6.737433688126059</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.192086064426348</v>
+        <v>-9.192086064426368</v>
       </c>
       <c r="L14" t="n">
-        <v>4.815893075864461</v>
+        <v>4.815893075864447</v>
       </c>
     </row>
   </sheetData>

--- a/example data/group/PCA ID Info.xlsx
+++ b/example data/group/PCA ID Info.xlsx
@@ -506,28 +506,28 @@
         <v>-12.77946573798521</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.077824292366595</v>
+        <v>-1.077824292366581</v>
       </c>
       <c r="F2" t="n">
-        <v>3.644491841383799</v>
+        <v>3.644491841383835</v>
       </c>
       <c r="G2" t="n">
-        <v>9.762032913970375</v>
+        <v>9.762032913970383</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7695414749914627</v>
+        <v>-0.7695414749914683</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2077380984430202</v>
+        <v>0.2077380984430383</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9361835552738</v>
+        <v>1.936183555273797</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1500622409348738</v>
+        <v>-0.1500622409348783</v>
       </c>
       <c r="L2" t="n">
-        <v>-5.119491778986665</v>
+        <v>-5.119491778986696</v>
       </c>
     </row>
     <row r="3">
@@ -540,34 +540,34 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.2164821253881</v>
+        <v>-10.21648212538811</v>
       </c>
       <c r="D3" t="n">
-        <v>-19.84343916631966</v>
+        <v>-19.84343916631968</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.192031130199647</v>
+        <v>-3.192031130199623</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03365031482844801</v>
+        <v>0.03365031482845154</v>
       </c>
       <c r="G3" t="n">
-        <v>11.67140028869544</v>
+        <v>11.67140028869545</v>
       </c>
       <c r="H3" t="n">
-        <v>3.375103645918346</v>
+        <v>3.375103645918449</v>
       </c>
       <c r="I3" t="n">
-        <v>-15.07373830871044</v>
+        <v>-15.07373830871042</v>
       </c>
       <c r="J3" t="n">
-        <v>1.814378537103339</v>
+        <v>1.814378537103467</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.117755933368068</v>
+        <v>-1.117755933368066</v>
       </c>
       <c r="L3" t="n">
-        <v>5.323130642169558</v>
+        <v>5.323130642169543</v>
       </c>
     </row>
     <row r="4">
@@ -580,34 +580,34 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.444596080811269</v>
+        <v>-1.444596080811263</v>
       </c>
       <c r="D4" t="n">
-        <v>-23.3604172607315</v>
+        <v>-23.36041726073152</v>
       </c>
       <c r="E4" t="n">
-        <v>1.302045975350598</v>
+        <v>1.302045975350634</v>
       </c>
       <c r="F4" t="n">
-        <v>1.533632607627437</v>
+        <v>1.533632607627451</v>
       </c>
       <c r="G4" t="n">
-        <v>1.521953593523712</v>
+        <v>1.521953593523714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6102376699202211</v>
+        <v>0.6102376699202086</v>
       </c>
       <c r="I4" t="n">
-        <v>8.139774912776552</v>
+        <v>8.139774912776469</v>
       </c>
       <c r="J4" t="n">
-        <v>-13.33327911250987</v>
+        <v>-13.33327911250998</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.15117800495447</v>
+        <v>-7.151178004954432</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.070571555912355</v>
+        <v>-3.070571555912327</v>
       </c>
     </row>
     <row r="5">
@@ -620,34 +620,34 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>23.02413070070061</v>
+        <v>23.02413070070054</v>
       </c>
       <c r="D5" t="n">
-        <v>-24.22948366881312</v>
+        <v>-24.22948366881315</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.4548356294664</v>
+        <v>-13.45483562946637</v>
       </c>
       <c r="F5" t="n">
-        <v>4.841997558552751</v>
+        <v>4.841997558552793</v>
       </c>
       <c r="G5" t="n">
-        <v>-12.20538569440608</v>
+        <v>-12.20538569440607</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7428088996382299</v>
+        <v>-0.742808899638273</v>
       </c>
       <c r="I5" t="n">
-        <v>1.906220601234352</v>
+        <v>1.906220601234408</v>
       </c>
       <c r="J5" t="n">
-        <v>6.044670824506506</v>
+        <v>6.044670824506527</v>
       </c>
       <c r="K5" t="n">
-        <v>8.665695909454316</v>
+        <v>8.665695909454309</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.735216679269467</v>
+        <v>-1.735216679269449</v>
       </c>
     </row>
     <row r="6">
@@ -660,34 +660,34 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90019129908539</v>
+        <v>14.90019129908537</v>
       </c>
       <c r="D6" t="n">
-        <v>13.93847314046838</v>
+        <v>13.93847314046836</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.898590194165674</v>
+        <v>-3.898590194165693</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.684496839462914</v>
+        <v>-6.684496839462912</v>
       </c>
       <c r="G6" t="n">
-        <v>4.304649135298023</v>
+        <v>4.304649135298034</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.882666499430949</v>
+        <v>-6.882666499430983</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.409882506393833</v>
+        <v>-2.409882506393793</v>
       </c>
       <c r="J6" t="n">
-        <v>8.931940978056293</v>
+        <v>8.931940978056268</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.564071409982654</v>
+        <v>-8.564071409982644</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.223067354887013</v>
+        <v>-7.223067354886986</v>
       </c>
     </row>
     <row r="7">
@@ -700,34 +700,34 @@
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>28.81828771394321</v>
+        <v>28.81828771394317</v>
       </c>
       <c r="D7" t="n">
         <v>15.20487920386134</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.311135479080217</v>
+        <v>-3.311135479080244</v>
       </c>
       <c r="F7" t="n">
         <v>11.23960451062889</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.668667828296781</v>
+        <v>-3.668667828296766</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.41453238564709</v>
+        <v>-10.41453238564701</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.601678128425647</v>
+        <v>-4.601678128425783</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.910074886208526</v>
+        <v>-7.910074886208529</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.063641743762971</v>
+        <v>-2.06364174376295</v>
       </c>
       <c r="L7" t="n">
-        <v>6.403576181832947</v>
+        <v>6.403576181832944</v>
       </c>
     </row>
     <row r="8">
@@ -740,34 +740,34 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.20013493090531</v>
+        <v>-10.2001349309053</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.391626237433782</v>
+        <v>-4.391626237433755</v>
       </c>
       <c r="E8" t="n">
         <v>16.14764470958401</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.709884212835991</v>
+        <v>-8.709884212836034</v>
       </c>
       <c r="G8" t="n">
-        <v>7.14737695158799</v>
+        <v>7.147376951588025</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.17407622006333</v>
+        <v>-12.17407622006336</v>
       </c>
       <c r="I8" t="n">
-        <v>9.641542000145835</v>
+        <v>9.641542000145821</v>
       </c>
       <c r="J8" t="n">
-        <v>4.905863425703561</v>
+        <v>4.905863425703485</v>
       </c>
       <c r="K8" t="n">
-        <v>4.347671495971918</v>
+        <v>4.347671495971915</v>
       </c>
       <c r="L8" t="n">
-        <v>5.972193891128915</v>
+        <v>5.972193891128921</v>
       </c>
     </row>
     <row r="9">
@@ -780,34 +780,34 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>12.11115778953774</v>
+        <v>12.11115778953771</v>
       </c>
       <c r="D9" t="n">
-        <v>16.2577422883586</v>
+        <v>16.25774228835854</v>
       </c>
       <c r="E9" t="n">
-        <v>-18.95566531416986</v>
+        <v>-18.95566531416994</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.78730822919664</v>
+        <v>-16.78730822919665</v>
       </c>
       <c r="G9" t="n">
-        <v>8.662388546502651</v>
+        <v>8.662388546502635</v>
       </c>
       <c r="H9" t="n">
-        <v>10.48590889791869</v>
+        <v>10.48590889791866</v>
       </c>
       <c r="I9" t="n">
-        <v>6.400849259721404</v>
+        <v>6.400849259721451</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.519908231360337</v>
+        <v>-2.51990823136034</v>
       </c>
       <c r="K9" t="n">
-        <v>2.716062485727717</v>
+        <v>2.716062485727706</v>
       </c>
       <c r="L9" t="n">
-        <v>2.985053744788936</v>
+        <v>2.985053744788911</v>
       </c>
     </row>
     <row r="10">
@@ -820,34 +820,34 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>1.817083333942913</v>
+        <v>1.817083333942888</v>
       </c>
       <c r="D10" t="n">
-        <v>15.35088729902666</v>
+        <v>15.35088729902673</v>
       </c>
       <c r="E10" t="n">
-        <v>12.58471028436294</v>
+        <v>12.58471028436299</v>
       </c>
       <c r="F10" t="n">
-        <v>24.4903840545206</v>
+        <v>24.49038405452059</v>
       </c>
       <c r="G10" t="n">
-        <v>7.053239619449712</v>
+        <v>7.053239619449682</v>
       </c>
       <c r="H10" t="n">
-        <v>9.773500272455005</v>
+        <v>9.773500272454969</v>
       </c>
       <c r="I10" t="n">
-        <v>3.22977856700754</v>
+        <v>3.229778567007626</v>
       </c>
       <c r="J10" t="n">
-        <v>2.217924637593029</v>
+        <v>2.217924637593036</v>
       </c>
       <c r="K10" t="n">
-        <v>3.500508890367648</v>
+        <v>3.500508890367642</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7500348588729776</v>
+        <v>-0.7500348588729528</v>
       </c>
     </row>
     <row r="11">
@@ -860,34 +860,34 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>-45.79877321826365</v>
+        <v>-45.79877321826373</v>
       </c>
       <c r="D11" t="n">
-        <v>11.40032260808425</v>
+        <v>11.40032260808422</v>
       </c>
       <c r="E11" t="n">
-        <v>-20.38522297087516</v>
+        <v>-20.38522297087512</v>
       </c>
       <c r="F11" t="n">
-        <v>8.508136004800411</v>
+        <v>8.508136004800422</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.154678070603008</v>
+        <v>-7.154678070602999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.334162850616992</v>
+        <v>-4.334162850617004</v>
       </c>
       <c r="I11" t="n">
-        <v>1.638764944133814</v>
+        <v>1.638764944133793</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5665490717198041</v>
+        <v>0.5665490717197724</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6401856483795617</v>
+        <v>-0.6401856483795604</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07848511890398098</v>
+        <v>0.07848511890398825</v>
       </c>
     </row>
     <row r="12">
@@ -900,34 +900,34 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.359968371778324</v>
+        <v>-4.359968371778302</v>
       </c>
       <c r="D12" t="n">
-        <v>9.560970558092432</v>
+        <v>9.560970558092434</v>
       </c>
       <c r="E12" t="n">
-        <v>13.37502778854409</v>
+        <v>13.3750277885441</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.663921056018194</v>
+        <v>-4.663921056018217</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.778740453326909</v>
+        <v>-3.778740453326908</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2416688878500512</v>
+        <v>-0.2416688878500159</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.393400151360981</v>
+        <v>-4.393400151361025</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.018563654818252</v>
+        <v>-4.018563654818218</v>
       </c>
       <c r="K12" t="n">
-        <v>4.908893290687752</v>
+        <v>4.908893290687753</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.569530233626406</v>
+        <v>-6.569530233626464</v>
       </c>
     </row>
     <row r="13">
@@ -940,34 +940,34 @@
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.708773208647825</v>
+        <v>-7.708773208647804</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5770800637631</v>
+        <v>5.577080063763108</v>
       </c>
       <c r="E13" t="n">
-        <v>9.494346537251252</v>
+        <v>9.494346537251229</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.26558479185656</v>
+        <v>-14.26558479185661</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.55458229281302</v>
+        <v>-8.554582292812995</v>
       </c>
       <c r="H13" t="n">
-        <v>1.914704841650648</v>
+        <v>1.914704841650704</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.914122203875047</v>
+        <v>-6.91412220387507</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.373118833185416</v>
+        <v>-5.373118833185367</v>
       </c>
       <c r="K13" t="n">
-        <v>4.74014897359959</v>
+        <v>4.74014897359961</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.110420193133892</v>
+        <v>-1.110420193133828</v>
       </c>
     </row>
     <row r="14">
@@ -980,34 +980,34 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0685213798997901</v>
+        <v>0.06852137989980712</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.685923090371475</v>
+        <v>-2.685923090371462</v>
       </c>
       <c r="E14" t="n">
-        <v>11.37152971523062</v>
+        <v>11.37152971523063</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.18070176297205</v>
+        <v>-3.180701762972086</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.76098670958218</v>
+        <v>-14.76098670958217</v>
       </c>
       <c r="H14" t="n">
-        <v>9.400001890375199</v>
+        <v>9.400001890375123</v>
       </c>
       <c r="I14" t="n">
-        <v>2.228152915303401</v>
+        <v>2.22815291530349</v>
       </c>
       <c r="J14" t="n">
-        <v>6.737433688126059</v>
+        <v>6.737433688126064</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.192086064426368</v>
+        <v>-9.192086064426395</v>
       </c>
       <c r="L14" t="n">
-        <v>4.815893075864447</v>
+        <v>4.815893075864405</v>
       </c>
     </row>
   </sheetData>

--- a/example data/group/PCA ID Info.xlsx
+++ b/example data/group/PCA ID Info.xlsx
@@ -500,34 +500,34 @@
         <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.010644281315046</v>
+        <v>-1.010644281315058</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.77946573798521</v>
+        <v>-12.77946573798519</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.077824292366581</v>
+        <v>-1.077824292366563</v>
       </c>
       <c r="F2" t="n">
-        <v>3.644491841383835</v>
+        <v>3.644491841383815</v>
       </c>
       <c r="G2" t="n">
-        <v>9.762032913970383</v>
+        <v>9.762032913970387</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7695414749914683</v>
+        <v>-0.7695414749914654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2077380984430383</v>
+        <v>0.2077380984430615</v>
       </c>
       <c r="J2" t="n">
-        <v>1.936183555273797</v>
+        <v>1.936183555273795</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1500622409348783</v>
+        <v>-0.1500622409348614</v>
       </c>
       <c r="L2" t="n">
-        <v>-5.119491778986696</v>
+        <v>-5.119491778986687</v>
       </c>
     </row>
     <row r="3">
@@ -543,31 +543,31 @@
         <v>-10.21648212538811</v>
       </c>
       <c r="D3" t="n">
-        <v>-19.84343916631968</v>
+        <v>-19.84343916631964</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.192031130199623</v>
+        <v>-3.192031130199616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03365031482845154</v>
+        <v>0.03365031482845839</v>
       </c>
       <c r="G3" t="n">
-        <v>11.67140028869545</v>
+        <v>11.67140028869544</v>
       </c>
       <c r="H3" t="n">
-        <v>3.375103645918449</v>
+        <v>3.375103645918461</v>
       </c>
       <c r="I3" t="n">
-        <v>-15.07373830871042</v>
+        <v>-15.07373830871037</v>
       </c>
       <c r="J3" t="n">
-        <v>1.814378537103467</v>
+        <v>1.814378537103614</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.117755933368066</v>
+        <v>-1.117755933368089</v>
       </c>
       <c r="L3" t="n">
-        <v>5.323130642169543</v>
+        <v>5.323130642169558</v>
       </c>
     </row>
     <row r="4">
@@ -580,34 +580,34 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.444596080811263</v>
+        <v>-1.444596080811273</v>
       </c>
       <c r="D4" t="n">
-        <v>-23.36041726073152</v>
+        <v>-23.36041726073149</v>
       </c>
       <c r="E4" t="n">
-        <v>1.302045975350634</v>
+        <v>1.302045975350628</v>
       </c>
       <c r="F4" t="n">
-        <v>1.533632607627451</v>
+        <v>1.533632607627463</v>
       </c>
       <c r="G4" t="n">
-        <v>1.521953593523714</v>
+        <v>1.521953593523724</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6102376699202086</v>
+        <v>0.6102376699201854</v>
       </c>
       <c r="I4" t="n">
-        <v>8.139774912776469</v>
+        <v>8.139774912776305</v>
       </c>
       <c r="J4" t="n">
-        <v>-13.33327911250998</v>
+        <v>-13.33327911251001</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.151178004954432</v>
+        <v>-7.15117800495447</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.070571555912327</v>
+        <v>-3.070571555912337</v>
       </c>
     </row>
     <row r="5">
@@ -620,34 +620,34 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>23.02413070070054</v>
+        <v>23.02413070070052</v>
       </c>
       <c r="D5" t="n">
-        <v>-24.22948366881315</v>
+        <v>-24.22948366881312</v>
       </c>
       <c r="E5" t="n">
         <v>-13.45483562946637</v>
       </c>
       <c r="F5" t="n">
-        <v>4.841997558552793</v>
+        <v>4.841997558552791</v>
       </c>
       <c r="G5" t="n">
-        <v>-12.20538569440607</v>
+        <v>-12.2053856944061</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.742808899638273</v>
+        <v>-0.742808899638276</v>
       </c>
       <c r="I5" t="n">
-        <v>1.906220601234408</v>
+        <v>1.906220601234446</v>
       </c>
       <c r="J5" t="n">
-        <v>6.044670824506527</v>
+        <v>6.044670824506458</v>
       </c>
       <c r="K5" t="n">
-        <v>8.665695909454309</v>
+        <v>8.66569590945433</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.735216679269449</v>
+        <v>-1.735216679269463</v>
       </c>
     </row>
     <row r="6">
@@ -660,34 +660,34 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90019129908537</v>
+        <v>14.9001912990854</v>
       </c>
       <c r="D6" t="n">
         <v>13.93847314046836</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.898590194165693</v>
+        <v>-3.898590194165679</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.684496839462912</v>
+        <v>-6.684496839462897</v>
       </c>
       <c r="G6" t="n">
-        <v>4.304649135298034</v>
+        <v>4.304649135298049</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.882666499430983</v>
+        <v>-6.882666499430946</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.409882506393793</v>
+        <v>-2.409882506393668</v>
       </c>
       <c r="J6" t="n">
-        <v>8.931940978056268</v>
+        <v>8.931940978056346</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.564071409982644</v>
+        <v>-8.564071409982636</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.223067354886986</v>
+        <v>-7.223067354886996</v>
       </c>
     </row>
     <row r="7">
@@ -700,34 +700,34 @@
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>28.81828771394317</v>
+        <v>28.81828771394318</v>
       </c>
       <c r="D7" t="n">
-        <v>15.20487920386134</v>
+        <v>15.20487920386132</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.311135479080244</v>
+        <v>-3.311135479080252</v>
       </c>
       <c r="F7" t="n">
-        <v>11.23960451062889</v>
+        <v>11.23960451062891</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.668667828296766</v>
+        <v>-3.668667828296764</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.41453238564701</v>
+        <v>-10.41453238564703</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.601678128425783</v>
+        <v>-4.601678128425847</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.910074886208529</v>
+        <v>-7.910074886208455</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.06364174376295</v>
+        <v>-2.063641743762988</v>
       </c>
       <c r="L7" t="n">
-        <v>6.403576181832944</v>
+        <v>6.403576181832952</v>
       </c>
     </row>
     <row r="8">
@@ -740,34 +740,34 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.2001349309053</v>
+        <v>-10.20013493090529</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.391626237433755</v>
+        <v>-4.391626237433758</v>
       </c>
       <c r="E8" t="n">
         <v>16.14764470958401</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.709884212836034</v>
+        <v>-8.709884212836016</v>
       </c>
       <c r="G8" t="n">
-        <v>7.147376951588025</v>
+        <v>7.147376951588022</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.17407622006336</v>
+        <v>-12.17407622006334</v>
       </c>
       <c r="I8" t="n">
-        <v>9.641542000145821</v>
+        <v>9.641542000145854</v>
       </c>
       <c r="J8" t="n">
-        <v>4.905863425703485</v>
+        <v>4.905863425703383</v>
       </c>
       <c r="K8" t="n">
-        <v>4.347671495971915</v>
+        <v>4.347671495971941</v>
       </c>
       <c r="L8" t="n">
-        <v>5.972193891128921</v>
+        <v>5.97219389112893</v>
       </c>
     </row>
     <row r="9">
@@ -780,34 +780,34 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>12.11115778953771</v>
+        <v>12.11115778953774</v>
       </c>
       <c r="D9" t="n">
         <v>16.25774228835854</v>
       </c>
       <c r="E9" t="n">
-        <v>-18.95566531416994</v>
+        <v>-18.95566531416987</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.78730822919665</v>
+        <v>-16.78730822919664</v>
       </c>
       <c r="G9" t="n">
-        <v>8.662388546502635</v>
+        <v>8.662388546502644</v>
       </c>
       <c r="H9" t="n">
         <v>10.48590889791866</v>
       </c>
       <c r="I9" t="n">
-        <v>6.400849259721451</v>
+        <v>6.400849259721415</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.51990823136034</v>
+        <v>-2.519908231360436</v>
       </c>
       <c r="K9" t="n">
-        <v>2.716062485727706</v>
+        <v>2.716062485727726</v>
       </c>
       <c r="L9" t="n">
-        <v>2.985053744788911</v>
+        <v>2.98505374478892</v>
       </c>
     </row>
     <row r="10">
@@ -820,34 +820,34 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>1.817083333942888</v>
+        <v>1.817083333942887</v>
       </c>
       <c r="D10" t="n">
-        <v>15.35088729902673</v>
+        <v>15.3508872990267</v>
       </c>
       <c r="E10" t="n">
         <v>12.58471028436299</v>
       </c>
       <c r="F10" t="n">
-        <v>24.49038405452059</v>
+        <v>24.49038405452065</v>
       </c>
       <c r="G10" t="n">
-        <v>7.053239619449682</v>
+        <v>7.053239619449657</v>
       </c>
       <c r="H10" t="n">
-        <v>9.773500272454969</v>
+        <v>9.773500272454966</v>
       </c>
       <c r="I10" t="n">
-        <v>3.229778567007626</v>
+        <v>3.229778567007618</v>
       </c>
       <c r="J10" t="n">
-        <v>2.217924637593036</v>
+        <v>2.21792463759297</v>
       </c>
       <c r="K10" t="n">
-        <v>3.500508890367642</v>
+        <v>3.50050889036766</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7500348588729528</v>
+        <v>-0.7500348588729657</v>
       </c>
     </row>
     <row r="11">
@@ -860,34 +860,34 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>-45.79877321826373</v>
+        <v>-45.79877321826374</v>
       </c>
       <c r="D11" t="n">
-        <v>11.40032260808422</v>
+        <v>11.40032260808424</v>
       </c>
       <c r="E11" t="n">
-        <v>-20.38522297087512</v>
+        <v>-20.38522297087509</v>
       </c>
       <c r="F11" t="n">
-        <v>8.508136004800422</v>
+        <v>8.5081360048004</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.154678070602999</v>
+        <v>-7.154678070602995</v>
       </c>
       <c r="H11" t="n">
         <v>-4.334162850617004</v>
       </c>
       <c r="I11" t="n">
-        <v>1.638764944133793</v>
+        <v>1.638764944133807</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5665490717197724</v>
+        <v>0.5665490717197638</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6401856483795604</v>
+        <v>-0.6401856483795614</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07848511890398825</v>
+        <v>0.07848511890397945</v>
       </c>
     </row>
     <row r="12">
@@ -903,31 +903,31 @@
         <v>-4.359968371778302</v>
       </c>
       <c r="D12" t="n">
-        <v>9.560970558092434</v>
+        <v>9.56097055809243</v>
       </c>
       <c r="E12" t="n">
-        <v>13.3750277885441</v>
+        <v>13.37502778854408</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.663921056018217</v>
+        <v>-4.663921056018223</v>
       </c>
       <c r="G12" t="n">
         <v>-3.778740453326908</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2416688878500159</v>
+        <v>-0.2416688878500255</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.393400151361025</v>
+        <v>-4.393400151361068</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.018563654818218</v>
+        <v>-4.0185636548182</v>
       </c>
       <c r="K12" t="n">
-        <v>4.908893290687753</v>
+        <v>4.908893290687729</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.569530233626464</v>
+        <v>-6.569530233626444</v>
       </c>
     </row>
     <row r="13">
@@ -940,34 +940,34 @@
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.708773208647804</v>
+        <v>-7.708773208647809</v>
       </c>
       <c r="D13" t="n">
-        <v>5.577080063763108</v>
+        <v>5.577080063763119</v>
       </c>
       <c r="E13" t="n">
-        <v>9.494346537251229</v>
+        <v>9.4943465372512</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.26558479185661</v>
+        <v>-14.26558479185662</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.554582292812995</v>
+        <v>-8.554582292813015</v>
       </c>
       <c r="H13" t="n">
-        <v>1.914704841650704</v>
+        <v>1.914704841650654</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.91412220387507</v>
+        <v>-6.914122203875152</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.373118833185367</v>
+        <v>-5.373118833185316</v>
       </c>
       <c r="K13" t="n">
-        <v>4.74014897359961</v>
+        <v>4.740148973599567</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.110420193133828</v>
+        <v>-1.11042019313386</v>
       </c>
     </row>
     <row r="14">
@@ -980,34 +980,34 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06852137989980712</v>
+        <v>0.06852137989978779</v>
       </c>
       <c r="D14" t="n">
         <v>-2.685923090371462</v>
       </c>
       <c r="E14" t="n">
-        <v>11.37152971523063</v>
+        <v>11.37152971523059</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.180701762972086</v>
+        <v>-3.180701762972078</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.76098670958217</v>
+        <v>-14.76098670958221</v>
       </c>
       <c r="H14" t="n">
-        <v>9.400001890375123</v>
+        <v>9.400001890375156</v>
       </c>
       <c r="I14" t="n">
-        <v>2.22815291530349</v>
+        <v>2.228152915303587</v>
       </c>
       <c r="J14" t="n">
-        <v>6.737433688126064</v>
+        <v>6.737433688126054</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.192086064426395</v>
+        <v>-9.192086064426356</v>
       </c>
       <c r="L14" t="n">
-        <v>4.815893075864405</v>
+        <v>4.815893075864417</v>
       </c>
     </row>
   </sheetData>
